--- a/NBIS.xlsx
+++ b/NBIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FB5E31-92C8-472E-A623-5435D41BC27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465EBD8D-7199-4204-82F8-8BE5D8325709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22035" yWindow="1770" windowWidth="18960" windowHeight="18495" xr2:uid="{AC62BB58-38E5-4FEB-A76D-4EBC5F30F9F7}"/>
+    <workbookView xWindow="10290" yWindow="900" windowWidth="17940" windowHeight="16280" xr2:uid="{AC62BB58-38E5-4FEB-A76D-4EBC5F30F9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>Price</t>
   </si>
@@ -97,13 +97,61 @@
   </si>
   <si>
     <t>Rent/Q</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Operating Income</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Product Development</t>
+  </si>
+  <si>
+    <t>COGS</t>
+  </si>
+  <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
+    <t>Gross Profit</t>
+  </si>
+  <si>
+    <t>SG&amp;A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -114,6 +162,13 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -135,10 +190,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -161,8 +217,18 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -497,10 +563,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E2C5C4-9000-4D8C-8AFC-9EFF7C3A2A69}">
-  <dimension ref="B2:M7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:M11"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>12</v>
       </c>
@@ -508,10 +574,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>13</v>
       </c>
@@ -519,44 +585,46 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>199.34011799999999</v>
+        <v>271.85521799999998</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K4" t="s">
         <v>2</v>
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>5382.1831859999993</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+        <v>74216.474514000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K5" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>2288.1999999999998</v>
+        <f>8042.1+1606.7</f>
+        <v>9648.8000000000011</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K6" t="s">
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>0</v>
+        <f>8499+46.7</f>
+        <v>8545.7000000000007</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -565,7 +633,24 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>3093.9831859999995</v>
+        <v>73113.374513999996</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="2">
+        <v>13045.2</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L11" s="1">
+        <f>+L7/L9</f>
+        <v>5.6046189030447975</v>
       </c>
     </row>
   </sheetData>
@@ -575,22 +660,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE64C1F8-DAFD-4C56-929D-DD43081EAF02}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="3"/>
-    <col min="5" max="5" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="3"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.1796875" style="3"/>
+    <col min="5" max="5" width="10.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
@@ -603,52 +688,199 @@
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="4" t="s">
+      <c r="G2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="10" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11">
         <v>43.3</v>
       </c>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E4" s="3">
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <v>105.1</v>
+      </c>
+      <c r="K3" s="10">
+        <v>582.29999999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13">
         <v>18.899999999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E5" s="3">
+      <c r="F4" s="13"/>
+      <c r="G4" s="12">
+        <v>30.1</v>
+      </c>
+      <c r="K4" s="12">
+        <v>133.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13">
         <f>+E3-E4</f>
         <v>24.4</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E6" s="3">
+      <c r="F5" s="13"/>
+      <c r="G5" s="12">
+        <v>75.2</v>
+      </c>
+      <c r="K5" s="12">
+        <v>259.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13">
         <v>34.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E7" s="3">
+      <c r="F6" s="13"/>
+      <c r="G6" s="12">
+        <f>+G3-G4-G5</f>
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="K6" s="12">
+        <f>+K3-K4-K5</f>
+        <v>188.99999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13">
         <v>53.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E8" s="3">
+      <c r="F7" s="13"/>
+      <c r="G7" s="12">
+        <v>68.2</v>
+      </c>
+      <c r="K7" s="12">
+        <v>173.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13">
         <f>+E6+E7</f>
         <v>87.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E9" s="3">
+      <c r="F8" s="13"/>
+      <c r="G8" s="12">
+        <v>42.8</v>
+      </c>
+      <c r="K8" s="12">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13">
         <f>+E5-E8</f>
         <v>-63.500000000000007</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F9" s="13"/>
+      <c r="G9" s="12">
+        <f t="shared" ref="G9:J9" si="0">+G7+G8</f>
+        <v>111</v>
+      </c>
+      <c r="H9" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="12">
+        <f>+K7+K8</f>
+        <v>364.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="12">
+        <f t="shared" ref="G10:J10" si="1">+G6-G9</f>
+        <v>-111.2</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="12">
+        <f>+K6-K9</f>
+        <v>-175.90000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>15</v>
       </c>
@@ -656,8 +888,32 @@
         <f>+E5/E3</f>
         <v>0.56351039260969982</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F13" s="6" t="e">
+        <f t="shared" ref="F13:K13" si="2">+F5/F3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="2"/>
+        <v>0.71550903901046625</v>
+      </c>
+      <c r="H13" s="6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I13" s="6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J13" s="6" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K13" s="6">
+        <f t="shared" si="2"/>
+        <v>0.44599003949854027</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -665,7 +921,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>17</v>
       </c>
@@ -674,7 +930,7 @@
         <v>11875</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>18</v>
       </c>
@@ -682,7 +938,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="21" spans="2:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:6" s="4" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -695,6 +951,9 @@
       <c r="F21" s="5"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{52A18441-6515-43A4-BCC3-B5EA8D8DFD4E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>